--- a/test/test_file.xlsx
+++ b/test/test_file.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsbie\Documents\Universiteit\Master\Jaar 2\MEP\Code\IbM-Fermentation\IbM-Fermentation\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C7157D-D2C0-44C1-A778-71E910CE760C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6F04E1-FE02-473E-A191-4EE01AB5FC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="808" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="808" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Information" sheetId="30" r:id="rId1"/>
@@ -26,11 +26,12 @@
     <sheet name="ThermoParam" sheetId="24" r:id="rId11"/>
     <sheet name="Ks" sheetId="31" r:id="rId12"/>
     <sheet name="Ki" sheetId="32" r:id="rId13"/>
-    <sheet name="Yield-Mu" sheetId="33" r:id="rId14"/>
-    <sheet name="ReactionMatrix" sheetId="21" r:id="rId15"/>
+    <sheet name="Kh" sheetId="35" r:id="rId14"/>
+    <sheet name="Yield-Mu" sheetId="33" r:id="rId15"/>
+    <sheet name="ReactionMatrix" sheetId="21" r:id="rId16"/>
   </sheets>
   <definedNames>
-    <definedName name="solver_adj" localSheetId="3" hidden="1">Parameters!$B$10</definedName>
+    <definedName name="solver_adj" localSheetId="3" hidden="1">Parameters!$B$13</definedName>
     <definedName name="solver_cvg" localSheetId="3" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="3" hidden="1">1</definedName>
@@ -44,7 +45,7 @@
     <definedName name="solver_nod" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_nwt" localSheetId="3" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="3" hidden="1">Parameters!$B$8</definedName>
+    <definedName name="solver_opt" localSheetId="3" hidden="1">Parameters!$B$10</definedName>
     <definedName name="solver_pre" localSheetId="3" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_rlx" localSheetId="3" hidden="1">2</definedName>
@@ -80,7 +81,7 @@
     <author>tc={873F5D62-7A36-441D-909B-5D8DF0BCC1F4}</author>
   </authors>
   <commentList>
-    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{873F5D62-7A36-441D-909B-5D8DF0BCC1F4}">
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{873F5D62-7A36-441D-909B-5D8DF0BCC1F4}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -144,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="290">
   <si>
     <t>AOB/AOA</t>
   </si>
@@ -1415,6 +1416,36 @@
   </si>
   <si>
     <t>Time (in simulation) between analysing balances</t>
+  </si>
+  <si>
+    <t>mol/L.bar</t>
+  </si>
+  <si>
+    <t>Set the Henry coefficient if necessary and indicate whether the compound is not transfered to the gas phase (0), aquaous and leaving (-1) or gaseous and entering (1). Make sure that all compounds are in the same order and have the same name as in the rest of the Excel file</t>
+  </si>
+  <si>
+    <t>kLa</t>
+  </si>
+  <si>
+    <t>Gas pressure</t>
+  </si>
+  <si>
+    <t>Representative gas volume</t>
+  </si>
+  <si>
+    <t>CALCULATED Representative gas volume of the modelled reactor. Based on a 75:25 liquid-gas ratio.</t>
+  </si>
+  <si>
+    <t>h-1</t>
+  </si>
+  <si>
+    <t>Volumetric Mass Transfer Coefficient</t>
+  </si>
+  <si>
+    <t>bar</t>
+  </si>
+  <si>
+    <t>Total gas pressure</t>
   </si>
 </sst>
 </file>
@@ -1766,7 +1797,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="85">
+  <borders count="88">
     <border>
       <left/>
       <right/>
@@ -2846,6 +2877,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2860,7 +2934,7 @@
     <xf numFmtId="0" fontId="35" fillId="11" borderId="39" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="279">
+  <cellXfs count="290">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="7"/>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="7" applyNumberFormat="1"/>
@@ -3606,6 +3680,39 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="2" fillId="11" borderId="85" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="41" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="2" fillId="11" borderId="86" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="2" fillId="11" borderId="87" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="52" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3622,9 +3729,33 @@
     <cellStyle name="Note" xfId="9" builtinId="10"/>
     <cellStyle name="Percent" xfId="8" builtinId="5"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="35">
     <dxf>
       <font>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
         <color theme="0" tint="-0.34998626667073579"/>
       </font>
     </dxf>
@@ -4178,7 +4309,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B11" dT="2021-12-16T15:08:36.62" personId="{969302A7-3B3A-4079-852A-4AE1C0564048}" id="{873F5D62-7A36-441D-909B-5D8DF0BCC1F4}">
+  <threadedComment ref="B14" dT="2021-12-16T15:08:36.62" personId="{969302A7-3B3A-4079-852A-4AE1C0564048}" id="{873F5D62-7A36-441D-909B-5D8DF0BCC1F4}">
     <text>Lemaire2008 -&gt; order of magnitude 30-80 g/L for synthetic feed, 150 g/L in their experiment</text>
   </threadedComment>
 </ThreadedComments>
@@ -4241,23 +4372,23 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A7">
-    <cfRule type="expression" dxfId="31" priority="6">
+    <cfRule type="expression" dxfId="34" priority="6">
       <formula>#REF! = FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="29" priority="4" operator="containsText" text="NA">
+    <cfRule type="containsText" dxfId="32" priority="4" operator="containsText" text="NA">
       <formula>NOT(ISERROR(SEARCH("NA",A8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="Inf">
+    <cfRule type="containsText" dxfId="31" priority="5" operator="containsText" text="Inf">
       <formula>NOT(ISERROR(SEARCH("Inf",A8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>$B$3&lt;&gt;"naive"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4745,19 +4876,19 @@
         <v>270</v>
       </c>
       <c r="B13" s="103">
-        <f>IF(COUNT(B2,C2)=2, EXP(($C$10+B2-C2)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(B2,C2)=2, EXP(($C$10+B2-C2)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="C13" s="100">
-        <f>IF(COUNT(C2,D2)=2, EXP((D2-C2)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(C2,D2)=2, EXP((D2-C2)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="D13" s="103">
-        <f>IF(COUNT(D2,E2)=2, EXP((E2-D2)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(D2,E2)=2, EXP((E2-D2)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="E13" s="103">
-        <f>IF(COUNT(E2,F2)=2, EXP((F2-E2)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(E2,F2)=2, EXP((F2-E2)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="H13" s="72"/>
@@ -4770,19 +4901,19 @@
         <v>271</v>
       </c>
       <c r="B14" s="103">
-        <f>IF(COUNT(B3,C3)=2, EXP(($C$10+B3-C3)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(B3,C3)=2, EXP(($C$10+B3-C3)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="C14" s="100">
-        <f>IF(COUNT(C3,D3)=2, EXP((D3-C3)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(C3,D3)=2, EXP((D3-C3)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="D14" s="103">
-        <f>IF(COUNT(D3,E3)=2, EXP((E3-D3)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(D3,E3)=2, EXP((E3-D3)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="E14" s="103">
-        <f>IF(COUNT(E3,F3)=2, EXP((F3-E3)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(E3,F3)=2, EXP((F3-E3)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="H14" s="72"/>
@@ -4793,19 +4924,19 @@
         <v>17</v>
       </c>
       <c r="B15" s="103">
-        <f>IF(COUNT(B4,C4)=2, EXP(($C$10+B4-C4)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(B4,C4)=2, EXP(($C$10+B4-C4)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="C15" s="100">
-        <f>IF(COUNT(C4,D4)=2, EXP((D4-C4)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(C4,D4)=2, EXP((D4-C4)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="D15" s="103">
-        <f>IF(COUNT(D4,E4)=2, EXP((E4-D4)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(D4,E4)=2, EXP((E4-D4)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="E15" s="103">
-        <f>IF(COUNT(E4,F4)=2, EXP((F4-E4)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(E4,F4)=2, EXP((F4-E4)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="H15" s="72"/>
@@ -4816,19 +4947,19 @@
         <v>83</v>
       </c>
       <c r="B16" s="103">
-        <f>IF(COUNT(B5,C5)=2, EXP(($C$10+B5-C5)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(B5,C5)=2, EXP(($C$10+B5-C5)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="C16" s="103">
-        <f>IF(COUNT(C5,D5)=2, EXP((D5-C5)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(C5,D5)=2, EXP((D5-C5)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="D16" s="103">
-        <f>IF(COUNT(D5,E5)=2, EXP((E5-D5)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(D5,E5)=2, EXP((E5-D5)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="E16" s="103">
-        <f>IF(COUNT(E5,F5)=2, EXP((F5-E5)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(E5,F5)=2, EXP((F5-E5)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="F16" s="71"/>
@@ -4842,15 +4973,15 @@
         <v>0</v>
       </c>
       <c r="C17" s="201">
-        <f>IF(COUNT(C6,D6)=2, EXP((D6-C6)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(C6,D6)=2, EXP((D6-C6)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="D17" s="201">
-        <f>IF(COUNT(D6,E6)=2, EXP((E6-D6)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(D6,E6)=2, EXP((E6-D6)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="E17" s="200">
-        <f>IF(COUNT(E6,F6)=2, EXP((F6-E6)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(E6,F6)=2, EXP((F6-E6)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="F17" s="71"/>
@@ -4865,15 +4996,15 @@
         <v>588.23529411764707</v>
       </c>
       <c r="C18" s="242">
-        <f>IF(COUNT(C7,D7)=2, EXP((D7-C7)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(C7,D7)=2, EXP((D7-C7)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>3.3901312221699524E-7</v>
       </c>
       <c r="D18" s="242">
-        <f>IF(COUNT(D7,E7)=2, EXP((E7-D7)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(D7,E7)=2, EXP((E7-D7)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>3.008575507210982E-11</v>
       </c>
       <c r="E18" s="243">
-        <f>IF(COUNT(E7,F7)=2, EXP((F7-E7)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(E7,F7)=2, EXP((F7-E7)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="F18" s="71"/>
@@ -4884,7 +5015,7 @@
         <v>78</v>
       </c>
       <c r="B19" s="200">
-        <f>IF(COUNT(B8,C8)=2, EXP(($C$10+B8-C8)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(B8,C8)=2, EXP(($C$10+B8-C8)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="C19" s="244">
@@ -4895,7 +5026,7 @@
         <v>1.2022644346174125E-2</v>
       </c>
       <c r="E19" s="200">
-        <f>IF(COUNT(E8,F8)=2, EXP((F8-E8)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(E8,F8)=2, EXP((F8-E8)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="F19" s="71"/>
@@ -4906,19 +5037,19 @@
         <v>79</v>
       </c>
       <c r="B20" s="243">
-        <f>IF(COUNT(B9,C9)=2, EXP(($C$10+B9-C9)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(B9,C9)=2, EXP(($C$10+B9-C9)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="C20" s="242">
-        <f>IF(COUNT(C9,D9)=2, EXP((D9-C9)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(C9,D9)=2, EXP((D9-C9)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="D20" s="242">
-        <f>IF(COUNT(D9,E9)=2, EXP((E9-D9)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(D9,E9)=2, EXP((E9-D9)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="E20" s="243">
-        <f>IF(COUNT(E9,F9)=2, EXP((F9-E9)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(E9,F9)=2, EXP((F9-E9)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="F20" s="71"/>
@@ -4929,19 +5060,19 @@
         <v>80</v>
       </c>
       <c r="B21" s="246">
-        <f>IF(COUNT(B10,C10)=2, EXP(($C$10+B10-C10)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(B10,C10)=2, EXP(($C$10+B10-C10)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="C21" s="184">
-        <f>IF(COUNT(C10,D10)=2, EXP((D10-C10)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(C10,D10)=2, EXP((D10-C10)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>5.845648305092005E-15</v>
       </c>
       <c r="D21" s="202">
-        <f>IF(COUNT(D10,E10)=2, EXP((E10-D10)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(D10,E10)=2, EXP((E10-D10)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="E21" s="202">
-        <f>IF(COUNT(E10,F10)=2, EXP((F10-E10)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(E10,F10)=2, EXP((F10-E10)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="F21" s="71"/>
@@ -4953,19 +5084,19 @@
         <v>18</v>
       </c>
       <c r="B22" s="103">
-        <f>IF(COUNT(B11,C11)=2, EXP(($C$10+B11-C11)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(B11,C11)=2, EXP(($C$10+B11-C11)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="C22" s="203">
-        <f>IF(COUNT(C11,D11)=2, EXP((D11-C11)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(C11,D11)=2, EXP((D11-C11)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="D22" s="203">
-        <f>IF(COUNT(D11,E11)=2, EXP((E11-D11)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(D11,E11)=2, EXP((E11-D11)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="E22" s="200">
-        <f>IF(COUNT(E11,F11)=2, EXP((F11-E11)/-(Parameters!$B$9*Parameters!$B$6)), 0)</f>
+        <f>IF(COUNT(E11,F11)=2, EXP((F11-E11)/-(Parameters!$B$12*Parameters!$B$6)), 0)</f>
         <v>0</v>
       </c>
       <c r="F22" s="71"/>
@@ -5201,37 +5332,37 @@
     <mergeCell ref="I24:I33"/>
   </mergeCells>
   <conditionalFormatting sqref="B18:B22 D19">
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="5" operator="containsText" text="NA">
+    <cfRule type="containsText" dxfId="13" priority="5" operator="containsText" text="NA">
       <formula>NOT(ISERROR(SEARCH("NA",B18)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="6" operator="containsText" text="Inf">
+    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="Inf">
       <formula>NOT(ISERROR(SEARCH("Inf",B18)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:E17 C18:D18 E18:E22">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F11 B13:E17 C18:D18 E18:E22 B24:F33">
-    <cfRule type="containsText" dxfId="7" priority="60" operator="containsText" text="NA">
+    <cfRule type="containsText" dxfId="10" priority="60" operator="containsText" text="NA">
       <formula>NOT(ISERROR(SEARCH("NA",B2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="61" operator="containsText" text="Inf">
+    <cfRule type="containsText" dxfId="9" priority="61" operator="containsText" text="Inf">
       <formula>NOT(ISERROR(SEARCH("Inf",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:D22">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="NA">
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="NA">
       <formula>NOT(ISERROR(SEARCH("NA",C20)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Inf">
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="Inf">
       <formula>NOT(ISERROR(SEARCH("Inf",C20)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5336,7 +5467,7 @@
   </mergeCells>
   <phoneticPr fontId="38" type="noConversion"/>
   <conditionalFormatting sqref="B2:E6">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5419,7 +5550,7 @@
     <mergeCell ref="E1:E4"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:D4">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5428,6 +5559,179 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEA04C96-24D4-44F4-AB2D-B9F0CE22F63A}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" customWidth="1"/>
+    <col min="5" max="5" width="63.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="77" t="s">
+        <v>270</v>
+      </c>
+      <c r="B1" s="279">
+        <v>0</v>
+      </c>
+      <c r="C1" s="90" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1" s="280">
+        <v>0</v>
+      </c>
+      <c r="E1" s="267" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="77" t="s">
+        <v>271</v>
+      </c>
+      <c r="B2" s="281">
+        <v>0</v>
+      </c>
+      <c r="C2" s="90" t="s">
+        <v>280</v>
+      </c>
+      <c r="D2" s="280">
+        <v>0</v>
+      </c>
+      <c r="E2" s="268"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="281">
+        <v>0</v>
+      </c>
+      <c r="C3" s="90" t="s">
+        <v>280</v>
+      </c>
+      <c r="D3" s="280">
+        <v>0</v>
+      </c>
+      <c r="E3" s="268"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="77" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="281">
+        <v>0</v>
+      </c>
+      <c r="C4" s="90" t="s">
+        <v>280</v>
+      </c>
+      <c r="D4" s="280">
+        <v>0</v>
+      </c>
+      <c r="E4" s="268"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="281">
+        <v>0</v>
+      </c>
+      <c r="C5" s="90" t="s">
+        <v>280</v>
+      </c>
+      <c r="D5" s="280">
+        <v>0</v>
+      </c>
+      <c r="E5" s="268"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="127" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="281">
+        <v>0</v>
+      </c>
+      <c r="C6" s="90" t="s">
+        <v>280</v>
+      </c>
+      <c r="D6" s="280">
+        <v>0</v>
+      </c>
+      <c r="E6" s="268"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="77" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="281">
+        <v>0</v>
+      </c>
+      <c r="C7" s="90" t="s">
+        <v>280</v>
+      </c>
+      <c r="D7" s="280">
+        <v>0</v>
+      </c>
+      <c r="E7" s="268"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="77" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="283">
+        <v>0</v>
+      </c>
+      <c r="C8" s="90" t="s">
+        <v>280</v>
+      </c>
+      <c r="D8" s="284">
+        <v>0</v>
+      </c>
+      <c r="E8" s="268"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="285"/>
+      <c r="B9" s="286"/>
+      <c r="C9" s="287"/>
+      <c r="D9" s="288"/>
+      <c r="E9" s="282"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="285"/>
+      <c r="B10" s="286"/>
+      <c r="C10" s="287"/>
+      <c r="D10" s="289"/>
+      <c r="E10" s="282"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="69"/>
+      <c r="D11" s="63"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E1:E10"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B1:B10">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="NA">
+      <formula>NOT(ISERROR(SEARCH("NA",B1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Inf">
+      <formula>NOT(ISERROR(SEARCH("Inf",B1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1">
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>#REF! = FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{765FFA51-252D-42F9-AC75-BD3B676D8AD2}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
@@ -5525,7 +5829,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
@@ -8391,27 +8695,27 @@
     <mergeCell ref="N27:Q27"/>
   </mergeCells>
   <conditionalFormatting sqref="S4:AG16">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S17:AJ23">
-    <cfRule type="cellIs" dxfId="25" priority="9" operator="notBetween">
+    <cfRule type="cellIs" dxfId="28" priority="9" operator="notBetween">
       <formula>0.0000000001</formula>
       <formula>-0.0000000001</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="10" operator="between">
+    <cfRule type="cellIs" dxfId="27" priority="10" operator="between">
       <formula>0.0000000001</formula>
       <formula>-0.0000000001</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH4:AI4">
-    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH5:AJ16">
-    <cfRule type="cellIs" dxfId="22" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8568,10 +8872,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.44140625" style="62" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" style="62" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" style="62" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.109375" style="62" customWidth="1"/>
     <col min="4" max="4" width="69.44140625" style="62" customWidth="1"/>
@@ -8685,99 +8989,125 @@
       </c>
       <c r="E7" s="69"/>
     </row>
-    <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" s="69" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="77" t="s">
+        <v>282</v>
+      </c>
+      <c r="B8" s="221">
+        <f>200/24</f>
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="C8" s="90" t="s">
+        <v>286</v>
+      </c>
+      <c r="D8" s="210" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="69" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="77" t="s">
+        <v>283</v>
+      </c>
+      <c r="B9" s="221">
+        <v>1.0129999999999999</v>
+      </c>
+      <c r="C9" s="90" t="s">
+        <v>288</v>
+      </c>
+      <c r="D9" s="210" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="77" t="s">
         <v>155</v>
       </c>
-      <c r="B8" s="222">
-        <f>B11/B12 * 4/3 * PI() *B10^3</f>
+      <c r="B10" s="222">
+        <f>B14/B15 * 4/3 * PI() *B13^3</f>
         <v>1.3962634015954636E-10</v>
       </c>
-      <c r="C8" s="90" t="s">
+      <c r="C10" s="90" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="210" t="s">
+      <c r="D10" s="210" t="s">
         <v>250</v>
       </c>
-      <c r="E8" s="69"/>
-    </row>
-    <row r="9" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="77" t="s">
+      <c r="E10" s="69"/>
+    </row>
+    <row r="11" spans="1:5" s="69" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="77" t="s">
+        <v>284</v>
+      </c>
+      <c r="B11" s="222">
+        <f>B10/3</f>
+        <v>4.6542113386515451E-11</v>
+      </c>
+      <c r="C11" s="90" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="210" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="77" t="s">
         <v>154</v>
       </c>
-      <c r="B9" s="223">
+      <c r="B12" s="223">
         <f>8.3144/1000</f>
         <v>8.3143999999999996E-3</v>
       </c>
-      <c r="C9" s="90" t="s">
+      <c r="C12" s="90" t="s">
         <v>223</v>
       </c>
-      <c r="D9" s="210" t="s">
+      <c r="D12" s="210" t="s">
         <v>154</v>
       </c>
-      <c r="E9" s="69"/>
-    </row>
-    <row r="10" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A10" s="174" t="s">
+      <c r="E12" s="69"/>
+    </row>
+    <row r="13" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A13" s="174" t="s">
         <v>251</v>
       </c>
-      <c r="B10" s="138">
+      <c r="B13" s="138">
         <v>1E-4</v>
       </c>
-      <c r="C10" s="90" t="s">
+      <c r="C13" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="224" t="s">
+      <c r="D13" s="224" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="77" t="s">
+    <row r="14" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="77" t="s">
         <v>276</v>
       </c>
-      <c r="B11" s="225">
+      <c r="B14" s="225">
         <v>100</v>
       </c>
-      <c r="C11" s="90" t="s">
+      <c r="C14" s="90" t="s">
         <v>253</v>
       </c>
-      <c r="D11" s="226" t="s">
+      <c r="D14" s="226" t="s">
         <v>254</v>
       </c>
-      <c r="E11" s="69"/>
-    </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="89" t="s">
+      <c r="E14" s="69"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="89" t="s">
         <v>277</v>
       </c>
-      <c r="B12" s="227">
+      <c r="B15" s="227">
         <v>3</v>
       </c>
-      <c r="C12" s="92" t="s">
+      <c r="C15" s="92" t="s">
         <v>253</v>
       </c>
-      <c r="D12" s="228" t="s">
+      <c r="D15" s="228" t="s">
         <v>255</v>
       </c>
-      <c r="E12" s="69"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13"/>
-      <c r="B13"/>
-      <c r="C13"/>
-      <c r="D13"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14"/>
-      <c r="B14"/>
-      <c r="C14"/>
-      <c r="D14"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15"/>
-      <c r="B15"/>
-      <c r="C15"/>
-      <c r="D15"/>
+      <c r="E15" s="69"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16"/>
@@ -8787,7 +9117,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17"/>
-      <c r="B17" s="189"/>
+      <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
     </row>
@@ -8796,22 +9126,25 @@
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
-      <c r="E18" s="94"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19"/>
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B20"/>
+      <c r="A20"/>
+      <c r="B20" s="189"/>
       <c r="C20"/>
       <c r="D20"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21"/>
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
+      <c r="E21" s="94"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B22"/>
@@ -8839,7 +9172,6 @@
       <c r="D26"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="69"/>
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
@@ -8854,14 +9186,30 @@
       <c r="C29"/>
       <c r="D29"/>
     </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="69"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:D1">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>$B$2=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:D4">
-    <cfRule type="expression" dxfId="20" priority="3">
+    <cfRule type="expression" dxfId="23" priority="3">
       <formula>$B$2 = FALSE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9344,7 +9692,7 @@
     <mergeCell ref="E16:E29"/>
   </mergeCells>
   <conditionalFormatting sqref="A17:D29">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>$B$16 = FALSE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9508,7 +9856,7 @@
     <mergeCell ref="E1:E8"/>
   </mergeCells>
   <conditionalFormatting sqref="E1">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>#REF! = FALSE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9778,22 +10126,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A7:D8">
-    <cfRule type="expression" dxfId="17" priority="2">
+    <cfRule type="expression" dxfId="20" priority="2">
       <formula>$B$6 ="suspension"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:D10">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>OR($B$6 = "granule", $B$6 = "mature granule")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:D15">
-    <cfRule type="expression" dxfId="15" priority="4">
+    <cfRule type="expression" dxfId="18" priority="4">
       <formula>$B$14&lt;&gt;"mechanistic"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:D16">
-    <cfRule type="expression" dxfId="14" priority="3">
+    <cfRule type="expression" dxfId="17" priority="3">
       <formula>$B$14&lt;&gt;"naive"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9992,12 +10340,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3:D4">
-    <cfRule type="expression" dxfId="13" priority="2">
+    <cfRule type="expression" dxfId="16" priority="2">
       <formula>$B$2=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:D12">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>$B$11=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
